--- a/dye_list.xlsx
+++ b/dye_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\단색 데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7854F9-CCDF-476B-BF50-1595603315A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61064C37-7365-4E98-BBB2-365D349AC39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA6203C8-CC7A-4AEC-9B1D-A75416B2CA87}"/>
+    <workbookView xWindow="690" yWindow="255" windowWidth="11025" windowHeight="15225" xr2:uid="{BA6203C8-CC7A-4AEC-9B1D-A75416B2CA87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="249">
   <si>
     <t>Black B 133%</t>
   </si>
@@ -192,619 +192,626 @@
     <t>Red RB 133%</t>
   </si>
   <si>
+    <t>Red SF-6BA</t>
+  </si>
+  <si>
+    <t>Red SN-2BL</t>
+  </si>
+  <si>
+    <t>Red SN-R</t>
+  </si>
+  <si>
+    <t>Red SPD conc.</t>
+  </si>
+  <si>
+    <t>SunBleach G/Yellow R</t>
+  </si>
+  <si>
+    <t>Suncion Red H-E3B</t>
+  </si>
+  <si>
+    <t>Sunfix Amber HP</t>
+  </si>
+  <si>
+    <t>Sunfix Black HP</t>
+  </si>
+  <si>
+    <t>Sunfix Black HPN</t>
+  </si>
+  <si>
+    <t>Sunfix Blue HP</t>
+  </si>
+  <si>
+    <t>Sunfix Blue MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Blue SPR</t>
+  </si>
+  <si>
+    <t>Sunfix Blue SPR-F</t>
+  </si>
+  <si>
+    <t>Sunfix Blue SSR</t>
+  </si>
+  <si>
+    <t>Sunfix Brown HP</t>
+  </si>
+  <si>
+    <t>Sunfix Cardinal HP</t>
+  </si>
+  <si>
+    <t>Sunfix Dark Blue EX</t>
+  </si>
+  <si>
+    <t>Sunfix Dark Blue SPD c</t>
+  </si>
+  <si>
+    <t>Sunfix Dark Blue SS</t>
+  </si>
+  <si>
+    <t>Sunfix Deep Red MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Deep Red SS</t>
+  </si>
+  <si>
+    <t>Sunfix Forest HP</t>
+  </si>
+  <si>
+    <t>Sunfix Grey SRL</t>
+  </si>
+  <si>
+    <t>Sunfix Lemon Yellow HP</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue CU</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue FE-BNA</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue HP</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue MF-GD</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue S2G</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SS</t>
+  </si>
+  <si>
+    <t>Sunfix Night S-R</t>
+  </si>
+  <si>
+    <t>Sunfix Olive IC</t>
+  </si>
+  <si>
+    <t>Sunfix Orange HP</t>
+  </si>
+  <si>
+    <t>Sunfix Orange MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Orange SS</t>
+  </si>
+  <si>
+    <t>Sunfix Red 6BH</t>
+  </si>
+  <si>
+    <t>Sunfix Red HP</t>
+  </si>
+  <si>
+    <t>Sunfix Red HP-2B</t>
+  </si>
+  <si>
+    <t>Sunfix Red MF-3G</t>
+  </si>
+  <si>
+    <t>Sunfix Red MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Red MF-GD conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Red SPR</t>
+  </si>
+  <si>
+    <t>Sunfix Red SPR-F</t>
+  </si>
+  <si>
+    <t>Sunfix Red SS-2B</t>
+  </si>
+  <si>
+    <t>Sunfix Red SSN</t>
+  </si>
+  <si>
+    <t>Sunfix Royal Blue FE-FR</t>
+  </si>
+  <si>
+    <t>Sunfix Ruby S3B</t>
+  </si>
+  <si>
+    <t>Sunfix Space HP</t>
+  </si>
+  <si>
+    <t>Sunfix Space SPD conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow Brown HP</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow HP</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow MF-CN</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow SS</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow SS conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow SSR</t>
+  </si>
+  <si>
+    <t>Sunfron Amber C-R</t>
+  </si>
+  <si>
+    <t>Sunfron Blue C-G</t>
+  </si>
+  <si>
+    <t>Sunfron Dark Blue SN-R</t>
+  </si>
+  <si>
+    <t>Sunfron Navy Blue SN-GN</t>
+  </si>
+  <si>
+    <t>Sunfron Orange C-R</t>
+  </si>
+  <si>
+    <t>Sunfron Orange SN-R</t>
+  </si>
+  <si>
+    <t>Sunfron Yellow C-4G</t>
+  </si>
+  <si>
+    <t>Sunzol Black 2RN conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black AF</t>
+  </si>
+  <si>
+    <t>Sunzol Black BN conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black EXPR</t>
+  </si>
+  <si>
+    <t>Sunzol Black FS</t>
+  </si>
+  <si>
+    <t>Sunzol Black RN conc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunzol Brill. Blue RS </t>
+  </si>
+  <si>
+    <t>sUNZOL RED 3B</t>
+  </si>
+  <si>
+    <t>Sunzol Red GRB</t>
+  </si>
+  <si>
+    <t>Sunzol Ultra Red GRB</t>
+  </si>
+  <si>
+    <t>Sunzol Ultra Yellow GR</t>
+  </si>
+  <si>
+    <t>Turquoise Blue G 133%</t>
+  </si>
+  <si>
+    <t>Turquoise Blue G 165%</t>
+  </si>
+  <si>
+    <t>Turquoise Blue G 266%</t>
+  </si>
+  <si>
+    <t>Turquoise Blue H-A</t>
+  </si>
+  <si>
+    <t>Violet 5RN</t>
+  </si>
+  <si>
+    <t>Yellow C-RG</t>
+  </si>
+  <si>
+    <t>Yellow EX</t>
+  </si>
+  <si>
+    <t>Yellow H-E4G</t>
+  </si>
+  <si>
+    <t>Yellow H-E4RN</t>
+  </si>
+  <si>
+    <t>Yellow H-E6GN</t>
+  </si>
+  <si>
+    <t>Yellow H-EL</t>
+  </si>
+  <si>
+    <t>Yellow SN-2R</t>
+  </si>
+  <si>
+    <t>Yellow SPD conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black B 133%</t>
+  </si>
+  <si>
+    <t>Sunzol Black CNN liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black DN conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black EXF</t>
+  </si>
+  <si>
+    <t>Sunzol Black FXB liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black GN conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black GXL liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black H-EM</t>
+  </si>
+  <si>
+    <t>Sunzol Black MT conc.</t>
+  </si>
+  <si>
+    <t>Sunzol Black MTL liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black NWD liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black NWR liq.</t>
+  </si>
+  <si>
+    <t>Sunzol Black ON4 liq.-1</t>
+  </si>
+  <si>
+    <t>Sunzol Black WN conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Blue EX</t>
+  </si>
+  <si>
+    <t>Sunfix Brill. Blue BB 133%</t>
+  </si>
+  <si>
+    <t>Sunfix Brill. Orange 3R</t>
+  </si>
+  <si>
+    <t>Sunfix Brill. Violet 5R</t>
+  </si>
+  <si>
+    <t>Sunfix Green 6B</t>
+  </si>
+  <si>
+    <t>Sunfix Green S4B</t>
+  </si>
+  <si>
+    <t>Sunfix Grey RL</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue EX</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue GG</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue MF-D</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue MF-RD</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SB</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SB conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SBF</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SGN</t>
+  </si>
+  <si>
+    <t>Sunfix Navy Blue SPD conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Orange MF-D</t>
+  </si>
+  <si>
+    <t>Sunfix Orange S2RN</t>
+  </si>
+  <si>
+    <t>Sunfix R&amp;D Red Sample</t>
+  </si>
+  <si>
+    <t>Sunfix Reactive Orange BR</t>
+  </si>
+  <si>
+    <t>Sunfix Red EX</t>
+  </si>
+  <si>
+    <t>Sunfix Red F3B</t>
+  </si>
+  <si>
+    <t>Sunfix Red MF-2BS</t>
+  </si>
+  <si>
+    <t>Sunfix Red MF-SB</t>
+  </si>
+  <si>
+    <t>Sunfix Red RB 133%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunfix Red S2B </t>
+  </si>
+  <si>
+    <t>Sunfix Red SF-6BA</t>
+  </si>
+  <si>
+    <t>Sunfix Red SPD conc.</t>
+  </si>
+  <si>
+    <t>Sunfix Turquoise Blue G 133%</t>
+  </si>
+  <si>
+    <t>Sunfix Turquoise Blue G 165%</t>
+  </si>
+  <si>
+    <t>Sunfix Turquoise Blue G 266%</t>
+  </si>
+  <si>
+    <t>Sunfix Violet 5RN</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow EX</t>
+  </si>
+  <si>
+    <t>Sunfix Yellow SPD conc.</t>
+  </si>
+  <si>
+    <t>Suncion Blue H-EGN 125%</t>
+  </si>
+  <si>
+    <t>Suncion Blue H-ERD 125%</t>
+  </si>
+  <si>
+    <t>Suncion Crimson H-EL</t>
+  </si>
+  <si>
+    <t>Suncion Green H-E4BD</t>
+  </si>
+  <si>
+    <t>Suncion Navy Blue H-ELN</t>
+  </si>
+  <si>
+    <t>Suncion Orange H-E2G</t>
+  </si>
+  <si>
+    <t>Suncion Orange H-ER</t>
+  </si>
+  <si>
+    <t>Suncion Red H-E7B</t>
+  </si>
+  <si>
+    <t>Suncion Red H-EGL</t>
+  </si>
+  <si>
+    <t>Suncion Turquoise Blue H-A</t>
+  </si>
+  <si>
+    <t>Suncion Yellow H-E4G</t>
+  </si>
+  <si>
+    <t>Suncion Yellow H-E4RN</t>
+  </si>
+  <si>
+    <t>Suncion Yellow H-E6GN</t>
+  </si>
+  <si>
+    <t>Suncion Yellow H-EL</t>
+  </si>
+  <si>
+    <t>Sunfron Orange C-R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Yellow C-RG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Navy Blue C-R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Blue C-R</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Red 3B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Blue SF-RL 200%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Red BSF 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Black B 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Black GSP 120%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix G/Yellow 2RN 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion Navy Blue H-ER 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunfix Orange S2R 150% </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Red BB 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Red S3B 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Scarlet S2G 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Yellow GR 100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Blue RS 100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Yellow S4GL 100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Blue SN-R</t>
+  </si>
+  <si>
+    <t>Sunfron Red SN-2BL</t>
+  </si>
+  <si>
+    <t>Sunfron Red SN-R</t>
+  </si>
+  <si>
+    <t>Sunfron Yellow SN-2R</t>
+  </si>
+  <si>
+    <t>Sunfix Dark Blue SPD conc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Red C-2BL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Red C-2G</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Red GRB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Navy Blue GRB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol G/Yellow GRB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Blue GRB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Ultra Yellow GRBN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Brown HP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Navy Blue H-ER 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron Red SN-2BL 01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yellow S4GL 100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">Red S2B </t>
-  </si>
-  <si>
-    <t>Red SF-6BA</t>
-  </si>
-  <si>
-    <t>Red SN-2BL</t>
-  </si>
-  <si>
-    <t>Red SN-R</t>
-  </si>
-  <si>
-    <t>Red SPD conc.</t>
-  </si>
-  <si>
-    <t>SunBleach G/Yellow R</t>
-  </si>
-  <si>
-    <t>Suncion Red H-E3B</t>
-  </si>
-  <si>
-    <t>Sunfix Amber HP</t>
-  </si>
-  <si>
-    <t>Sunfix Black HP</t>
-  </si>
-  <si>
-    <t>Sunfix Black HPN</t>
-  </si>
-  <si>
-    <t>Sunfix Blue HP</t>
-  </si>
-  <si>
-    <t>Sunfix Blue MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Blue SPR</t>
-  </si>
-  <si>
-    <t>Sunfix Blue SPR-F</t>
-  </si>
-  <si>
-    <t>Sunfix Blue SSR</t>
-  </si>
-  <si>
-    <t>Sunfix Brown HP</t>
-  </si>
-  <si>
-    <t>Sunfix Cardinal HP</t>
-  </si>
-  <si>
-    <t>Sunfix Dark Blue EX</t>
-  </si>
-  <si>
-    <t>Sunfix Dark Blue SPD c</t>
-  </si>
-  <si>
-    <t>Sunfix Dark Blue SS</t>
-  </si>
-  <si>
-    <t>Sunfix Deep Red MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Deep Red SS</t>
-  </si>
-  <si>
-    <t>Sunfix Forest HP</t>
-  </si>
-  <si>
-    <t>Sunfix Grey SRL</t>
-  </si>
-  <si>
-    <t>Sunfix Lemon Yellow HP</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue CU</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue FE-BNA</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue HP</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue MF-GD</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue S2G</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SS</t>
-  </si>
-  <si>
-    <t>Sunfix Night S-R</t>
-  </si>
-  <si>
-    <t>Sunfix Olive IC</t>
-  </si>
-  <si>
-    <t>Sunfix Orange HP</t>
-  </si>
-  <si>
-    <t>Sunfix Orange MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Orange SS</t>
-  </si>
-  <si>
-    <t>Sunfix Red 6BH</t>
-  </si>
-  <si>
-    <t>Sunfix Red HP</t>
-  </si>
-  <si>
-    <t>Sunfix Red HP-2B</t>
-  </si>
-  <si>
-    <t>Sunfix Red MF-3G</t>
-  </si>
-  <si>
-    <t>Sunfix Red MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Red MF-GD conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Red SPR</t>
-  </si>
-  <si>
-    <t>Sunfix Red SPR-F</t>
-  </si>
-  <si>
-    <t>Sunfix Red SS-2B</t>
-  </si>
-  <si>
-    <t>Sunfix Red SSN</t>
-  </si>
-  <si>
-    <t>Sunfix Royal Blue FE-FR</t>
-  </si>
-  <si>
-    <t>Sunfix Ruby S3B</t>
-  </si>
-  <si>
-    <t>Sunfix Space HP</t>
-  </si>
-  <si>
-    <t>Sunfix Space SPD conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow Brown HP</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow HP</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow MF-CN</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow SS</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow SS conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow SSR</t>
-  </si>
-  <si>
-    <t>Sunfron Amber C-R</t>
-  </si>
-  <si>
-    <t>Sunfron Blue C-G</t>
-  </si>
-  <si>
-    <t>Sunfron Dark Blue SN-R</t>
-  </si>
-  <si>
-    <t>Sunfron Navy Blue SN-GN</t>
-  </si>
-  <si>
-    <t>Sunfron Orange C-R</t>
-  </si>
-  <si>
-    <t>Sunfron Orange SN-R</t>
-  </si>
-  <si>
-    <t>Sunfron Yellow C-4G</t>
-  </si>
-  <si>
-    <t>Sunzol Black 2RN conc.</t>
-  </si>
-  <si>
-    <t>Sunzol Black AF</t>
-  </si>
-  <si>
-    <t>Sunzol Black BN conc.</t>
-  </si>
-  <si>
-    <t>Sunzol Black EXPR</t>
-  </si>
-  <si>
-    <t>Sunzol Black FS</t>
-  </si>
-  <si>
-    <t>Sunzol Black RN conc.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red S3B 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scarlet S2G 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black B 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black GSP 120%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black ON400 liq.-001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>G/Yellow 2RN 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red BB 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red BSF 150%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Sunzol Brill. Blue RS </t>
-  </si>
-  <si>
-    <t>sUNZOL RED 3B</t>
-  </si>
-  <si>
-    <t>Sunzol Red GRB</t>
-  </si>
-  <si>
-    <t>Sunzol Ultra Red GRB</t>
-  </si>
-  <si>
-    <t>Sunzol Ultra Yellow GR</t>
-  </si>
-  <si>
-    <t>Turquoise Blue G 133%</t>
-  </si>
-  <si>
-    <t>Turquoise Blue G 165%</t>
-  </si>
-  <si>
-    <t>Turquoise Blue G 266%</t>
-  </si>
-  <si>
-    <t>Turquoise Blue H-A</t>
-  </si>
-  <si>
-    <t>Violet 5RN</t>
-  </si>
-  <si>
-    <t>Yellow C-RG</t>
-  </si>
-  <si>
-    <t>Yellow EX</t>
-  </si>
-  <si>
-    <t>Yellow H-E4G</t>
-  </si>
-  <si>
-    <t>Yellow H-E4RN</t>
-  </si>
-  <si>
-    <t>Yellow H-E6GN</t>
-  </si>
-  <si>
-    <t>Yellow H-EL</t>
-  </si>
-  <si>
-    <t>Yellow SN-2R</t>
-  </si>
-  <si>
-    <t>Yellow SPD conc.</t>
-  </si>
-  <si>
-    <t>Black B 15%</t>
-  </si>
-  <si>
-    <t>Black GSP 12%</t>
-  </si>
-  <si>
-    <t>Black ON4 liq.-1</t>
-  </si>
-  <si>
-    <t>G/Yellow 2RN 15%</t>
-  </si>
-  <si>
-    <t>Navy Blue H-ER 15%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange S2R 15% </t>
-  </si>
-  <si>
-    <t>Red BB 15%</t>
-  </si>
-  <si>
-    <t>Red BSF 15%</t>
-  </si>
-  <si>
-    <t>Red S3B 15%</t>
-  </si>
-  <si>
-    <t>Scarlet S2G 15%</t>
-  </si>
-  <si>
-    <t>Sunfix Blue SF-RL 2%</t>
-  </si>
-  <si>
-    <t>Sunfron Red SN-2BL 1</t>
-  </si>
-  <si>
-    <t>Sunzol Blue RS 1%</t>
-  </si>
-  <si>
-    <t>Sunzol Yellow GR 1%</t>
-  </si>
-  <si>
-    <t>Yellow S4GL 1%</t>
-  </si>
-  <si>
-    <t>Sunzol Black B 133%</t>
-  </si>
-  <si>
-    <t>Sunzol Black CNN liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black DN conc.</t>
-  </si>
-  <si>
-    <t>Sunzol Black EXF</t>
-  </si>
-  <si>
-    <t>Sunzol Black FXB liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black GN conc.</t>
-  </si>
-  <si>
-    <t>Sunzol Black GXL liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black H-EM</t>
-  </si>
-  <si>
-    <t>Sunzol Black MT conc.</t>
-  </si>
-  <si>
-    <t>Sunzol Black MTL liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black NWD liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black NWR liq.</t>
-  </si>
-  <si>
-    <t>Sunzol Black ON4 liq.-1</t>
-  </si>
-  <si>
-    <t>Sunzol Black WN conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Blue EX</t>
-  </si>
-  <si>
-    <t>Sunfix Brill. Blue BB 133%</t>
-  </si>
-  <si>
-    <t>Sunfix Brill. Orange 3R</t>
-  </si>
-  <si>
-    <t>Sunfix Brill. Violet 5R</t>
-  </si>
-  <si>
-    <t>Sunfix Green 6B</t>
-  </si>
-  <si>
-    <t>Sunfix Green S4B</t>
-  </si>
-  <si>
-    <t>Sunfix Grey RL</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue EX</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue GG</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue MF-D</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue MF-RD</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SB</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SB conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SBF</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SGN</t>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SPD conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Orange MF-D</t>
-  </si>
-  <si>
-    <t>Sunfix Orange S2RN</t>
-  </si>
-  <si>
-    <t>Sunfix R&amp;D Red Sample</t>
-  </si>
-  <si>
-    <t>Sunfix Reactive Orange BR</t>
-  </si>
-  <si>
-    <t>Sunfix Red EX</t>
-  </si>
-  <si>
-    <t>Sunfix Red F3B</t>
-  </si>
-  <si>
-    <t>Sunfix Red MF-2BS</t>
-  </si>
-  <si>
-    <t>Sunfix Red MF-SB</t>
-  </si>
-  <si>
-    <t>Sunfix Red RB 133%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunfix Red S2B </t>
-  </si>
-  <si>
-    <t>Sunfix Red SF-6BA</t>
-  </si>
-  <si>
-    <t>Sunfix Red SPD conc.</t>
-  </si>
-  <si>
-    <t>Sunfix Turquoise Blue G 133%</t>
-  </si>
-  <si>
-    <t>Sunfix Turquoise Blue G 165%</t>
-  </si>
-  <si>
-    <t>Sunfix Turquoise Blue G 266%</t>
-  </si>
-  <si>
-    <t>Sunfix Violet 5RN</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow EX</t>
-  </si>
-  <si>
-    <t>Sunfix Yellow SPD conc.</t>
-  </si>
-  <si>
-    <t>Suncion Blue H-EGN 125%</t>
-  </si>
-  <si>
-    <t>Suncion Blue H-ERD 125%</t>
-  </si>
-  <si>
-    <t>Suncion Crimson H-EL</t>
-  </si>
-  <si>
-    <t>Suncion Green H-E4BD</t>
-  </si>
-  <si>
-    <t>Suncion Navy Blue H-ELN</t>
-  </si>
-  <si>
-    <t>Suncion Orange H-E2G</t>
-  </si>
-  <si>
-    <t>Suncion Orange H-ER</t>
-  </si>
-  <si>
-    <t>Suncion Red H-E7B</t>
-  </si>
-  <si>
-    <t>Suncion Red H-EGL</t>
-  </si>
-  <si>
-    <t>Suncion Turquoise Blue H-A</t>
-  </si>
-  <si>
-    <t>Suncion Yellow H-E4G</t>
-  </si>
-  <si>
-    <t>Suncion Yellow H-E4RN</t>
-  </si>
-  <si>
-    <t>Suncion Yellow H-E6GN</t>
-  </si>
-  <si>
-    <t>Suncion Yellow H-EL</t>
-  </si>
-  <si>
-    <t>Sunfron Orange C-R</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Yellow C-RG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Navy Blue C-R</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Blue C-R</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Red 3B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Blue SF-RL 200%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Red BSF 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Black B 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Black GSP 120%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix G/Yellow 2RN 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suncion Navy Blue H-ER 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunfix Orange S2R 150% </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Red BB 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Red S3B 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Scarlet S2G 150%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Yellow GR 100%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Blue RS 100%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Yellow S4GL 100%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Blue SN-R</t>
-  </si>
-  <si>
-    <t>Sunfron Red SN-2BL</t>
-  </si>
-  <si>
-    <t>Sunfron Red SN-R</t>
-  </si>
-  <si>
-    <t>Sunfron Yellow SN-2R</t>
-  </si>
-  <si>
-    <t>Sunfix Dark Blue SPD conc.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Red C-2BL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfron Red C-2G</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Red GRB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Navy Blue GRB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol G/Yellow GRB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Blue GRB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunzol Ultra Yellow GRBN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Brown HP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange S2R 150% </t>
   </si>
 </sst>
 </file>
@@ -1200,34 +1207,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1235,7 +1242,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1243,7 +1250,7 @@
         <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1251,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1259,15 +1266,15 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1275,7 +1282,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1283,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1291,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1299,15 +1306,15 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1315,15 +1322,15 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>147</v>
+        <v>235</v>
       </c>
       <c r="B16" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1331,51 +1338,51 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -1384,93 +1391,93 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -1479,16 +1486,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F35" s="2"/>
     </row>
@@ -1497,7 +1504,7 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F36" s="1"/>
     </row>
@@ -1506,7 +1513,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="F37" s="1"/>
     </row>
@@ -1515,16 +1522,16 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F39" s="1"/>
     </row>
@@ -1533,241 +1540,241 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F47" s="2"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -1776,7 +1783,7 @@
         <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="F67" s="2"/>
     </row>
@@ -1785,7 +1792,7 @@
         <v>52</v>
       </c>
       <c r="B68" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="F68" s="1"/>
     </row>
@@ -1794,25 +1801,25 @@
         <v>53</v>
       </c>
       <c r="B69" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F71" s="1"/>
     </row>
@@ -1821,7 +1828,7 @@
         <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -1830,34 +1837,34 @@
         <v>34</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -1866,52 +1873,52 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F77" s="1"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="F79" s="1"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="F81" s="1"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -1920,16 +1927,16 @@
         <v>26</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="F83" s="1"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F84" s="2"/>
     </row>
@@ -1938,7 +1945,7 @@
         <v>35</v>
       </c>
       <c r="B85" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F85" s="1"/>
     </row>
@@ -1947,7 +1954,7 @@
         <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F86" s="1"/>
     </row>
@@ -1956,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F87" s="1"/>
     </row>
@@ -1965,70 +1972,70 @@
         <v>38</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="F88" s="1"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F90" s="2"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B93" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B95" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F95" s="1"/>
     </row>
@@ -2037,7 +2044,7 @@
         <v>46</v>
       </c>
       <c r="B96" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="F96" s="1"/>
     </row>
@@ -2046,16 +2053,16 @@
         <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="F97" s="2"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F98" s="1"/>
     </row>
@@ -2064,7 +2071,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="F99" s="2"/>
     </row>
@@ -2073,86 +2080,86 @@
         <v>28</v>
       </c>
       <c r="B100" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F100" s="1"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F101" s="2"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F102" s="2"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F103" s="2"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F106" s="1"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B107" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -2160,25 +2167,25 @@
         <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F110" s="2"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F111" s="1"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F112" s="1"/>
     </row>
@@ -2187,7 +2194,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -2196,7 +2203,7 @@
         <v>31</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="F114" s="1"/>
     </row>
@@ -2205,15 +2212,15 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>143</v>
+        <v>241</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -2221,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -2229,7 +2236,7 @@
         <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -2237,7 +2244,7 @@
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -2245,15 +2252,15 @@
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="B121" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -2261,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -2269,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -2277,7 +2284,7 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -2285,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="B125" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -2293,15 +2300,15 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>145</v>
+        <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -2309,47 +2316,47 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B129" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B130" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
@@ -2357,7 +2364,7 @@
         <v>19</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -2365,7 +2372,7 @@
         <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
@@ -2373,15 +2380,15 @@
         <v>21</v>
       </c>
       <c r="B136" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="B137" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
@@ -2389,7 +2396,7 @@
         <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
@@ -2397,7 +2404,7 @@
         <v>27</v>
       </c>
       <c r="B139" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
@@ -2405,7 +2412,7 @@
         <v>30</v>
       </c>
       <c r="B140" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
@@ -2413,7 +2420,7 @@
         <v>44</v>
       </c>
       <c r="B141" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
@@ -2421,23 +2428,23 @@
         <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="B143" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="B144" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -2445,7 +2452,7 @@
         <v>49</v>
       </c>
       <c r="B145" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -2453,103 +2460,103 @@
         <v>54</v>
       </c>
       <c r="B146" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B147" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B148" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B149" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B150" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="B151" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>125</v>
+        <v>247</v>
       </c>
       <c r="B152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B153" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="B154" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B155" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B156" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B157" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B158" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
